--- a/Snapshot Metric.xlsx
+++ b/Snapshot Metric.xlsx
@@ -3808,7 +3808,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>actual</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>actual</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>actual</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>actual</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>actual</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">

--- a/Snapshot Metric.xlsx
+++ b/Snapshot Metric.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4932,6 +4932,246 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>LP Equity</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Investment Basis</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Limited partner's equity contribution to the deal</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Acquisition model, equity waterfall, LP agreement</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>projection</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>What is the LP/GP equity structure?</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>LP Equity; LP Contribution; LP Capital; Limited Partner Equity; LP Equity Check</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>GP Equity / Sponsor Equity</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Investment Basis</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>General partner's (sponsor's) equity contribution to the deal</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Acquisition model, equity waterfall, operating agreement</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>projection</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>What is the LP/GP equity structure?</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>GP Equity; Sponsor Equity; GP Contribution; Sponsor Contribution; General Partner Equity; GP Co-invest; Co-GP Equity</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Preferred Return</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Valuation &amp; Returns</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Minimum return threshold LP must receive before GP participates in upside (promote)</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Acquisition model, equity waterfall, LP agreement</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>projection</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>What is the LP/GP equity structure?</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Preferred Return; Pref Return; LP Preferred Return; Preferred Yield; Hurdle Rate; LP Hurdle; Pref</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>GP Promote</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Valuation &amp; Returns</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>GP's carried interest / promote above the preferred return hurdle</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Acquisition model, equity waterfall</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>projection</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>What is the LP/GP equity structure?</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>GP Promote; Promote; Carried Interest; GP Carry; Carry; Promote Structure; Performance Fee</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>LP / GP Split</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Investment Basis</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Percentage ownership split between limited partner(s) and general partner</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Acquisition model, operating agreement</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>projection</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>What is the LP/GP equity structure?</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>LP/GP Split; LP / GP Split; Equity Split; Ownership Split; GP/LP Split; LP Ownership; GP Ownership</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Snapshot Metric.xlsx
+++ b/Snapshot Metric.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J92"/>
+  <dimension ref="A1:J94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -731,7 +731,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Total Project Cost</t>
+          <t>Total Project Cost; Total Development Cost; All-in Cost; Total All-in Cost; Total Cost</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Equity Invested</t>
+          <t>Equity Invested; Total Equity; Equity Check; Equity; Total Equity Invested</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Going-in Cap Rate; Capitalization Rate; Going-In Cap; Purchase Cap Rate; Cap Rate</t>
+          <t>Going-in Cap Rate; Going-In Cap; Purchase Cap Rate; Acquisition Cap Rate</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Stabilized Yield on Cost; Yield on Cost (Stabilized); Stabilized YOC</t>
+          <t>Stabilized Yield on Cost; Yield on Cost (Stabilized); Stabilized YOC; Return on Cost; Untrended Return on Cost</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Lease-up Cost per Occupied SF/Unit; Lease-up Cost per Occupied SF; Unit</t>
+          <t>Lease-up Cost per Occupied SF/Unit; Lease-Up Cost per Unit; Leasing Cost per Unit</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Levered IRR; IRR (Levered); Equity IRR</t>
+          <t>Levered IRR; IRR; IRR (Levered); Equity IRR; Project IRR</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4978,7 +4978,6 @@
           <t>LP Equity; LP Contribution; LP Capital; Limited Partner Equity; LP Equity Check</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5026,7 +5025,6 @@
           <t>GP Equity; Sponsor Equity; GP Contribution; Sponsor Contribution; General Partner Equity; GP Co-invest; Co-GP Equity</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5074,7 +5072,6 @@
           <t>Preferred Return; Pref Return; LP Preferred Return; Preferred Yield; Hurdle Rate; LP Hurdle; Pref</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5122,7 +5119,6 @@
           <t>GP Promote; Promote; Carried Interest; GP Carry; Carry; Promote Structure; Performance Fee</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5170,7 +5166,105 @@
           <t>LP/GP Split; LP / GP Split; Equity Split; Ownership Split; GP/LP Split; LP Ownership; GP Ownership</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Exit Cap Rate</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Valuation &amp; Returns</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Capitalization rate applied to exit-year NOI to compute sale value</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Acquisition model, underwriting proforma</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>projection</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>What is the exit assumption?</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Exit Cap Rate; Exit Cap; Cap Rate at Exit; Disposition Cap Rate; Sale Cap Rate; Terminal Cap Rate; Reversion Cap Rate</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Exit NOI / Exit Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Hold Period</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Investment Basis</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Planned duration from acquisition/closing to disposition, in years</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Acquisition model, underwriting proforma</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>projection</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>What is the deal structure?</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Hold Period; Holding Period; Investment Period; Project Timeline; Total Project Timeline</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Snapshot Metric.xlsx
+++ b/Snapshot Metric.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J94"/>
+  <dimension ref="A1:J96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5266,6 +5266,100 @@
         </is>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Total Units</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Investment Basis</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Total number of residential, hotel, or commercial units in the asset</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Acquisition model, rent roll, offering memorandum</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>What is the asset?</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Total Units; Total # of Units; Number of Units; Unit Count; Total Unit Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Total SF</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Investment Basis</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Total gross square footage of the asset</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Acquisition model, rent roll, offering memorandum</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>What is the asset?</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Total SF; Total Gross SF; Gross SF; Total Square Feet; Gross Square Feet; Total GLA; Rentable SF; Total Rentable SF; NRA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Snapshot Metric.xlsx
+++ b/Snapshot Metric.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J96"/>
+  <dimension ref="A1:J99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -575,7 +575,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Closing Costs; Transaction Costs; Acquisition Costs; Due Diligence Costs; Transfer Tax; Title Insurance; Legal Fees; Closing &amp; Transaction Costs; Soft Costs at Close</t>
+          <t>Closing Costs; Transaction Costs; Due Diligence Costs; Transfer Tax; Title Insurance; Legal Fees; Closing &amp; Transaction Costs; Soft Costs at Close</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>extracted</t>
+          <t>calculated</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Total Project Cost; Total Development Cost; All-in Cost; Total All-in Cost; Total Cost; Total Uses; Total Project Budget; Gross Project Cost; Total Investment; Development Budget</t>
+          <t>Total Project Cost; Total Development Cost; All-in Cost; Total All-in Cost; Total Cost</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Potential Gross Revenue (PGR) / Potential Gross Income (PGI); Potential Gross Revenue; Potential Gross Income; PGR; PGI; Gross Potential Revenue; Gross Potential Income; Gross Potential Rent; Scheduled Rent; Potential Rental Revenue; Scheduled Rental Revenue; GPR; Gross Rent; Market Rent Total; Gross Revenue; Total Scheduled Income</t>
+          <t>Potential Gross Revenue (PGR) / Potential Gross Income (PGI); Potential Gross Revenue; Potential Gross Income; PGR; PGI; Gross Potential Revenue; Gross Potential Income; Potential Rental Revenue; Scheduled Rent; Scheduled Rental Revenue; GPR; Total Scheduled Income</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Operating Expenses; OpEx; Total Operating Expenses; Operating Expense; Total Expenses; Operating Costs; Total Operating Costs; G&amp;A; General &amp; Administrative; Property Operating Expenses; Operating &amp; Maintenance; Expenses Before Debt Service</t>
+          <t>Operating Expenses; OpEx; Total Operating Expenses; Operating Expense; Total Expenses; Operating Costs; Total Operating Costs; Property Operating Expenses; Operating &amp; Maintenance; Expenses Before Debt Service</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Physical Occupancy; Occupancy Rate; Physical Occ; Occupancy %; Current Occupancy; Occupied %; Occupancy; Physical Occ %</t>
+          <t>Physical Occupancy; Occupancy Rate; Physical Occ; Current Occupancy; Occupied Units; Physical Occ %</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Total Units; Total # of Units; Number of Units; Unit Count; Total Unit Count; Residential Units; Apartment Units; # Apartments; Total Apartments; Units; Doors; Keys; Total Keys; Total Rooms; Total Beds; Keys / Rooms; Hotel Rooms</t>
+          <t>Total Units; Total # of Units; Number of Units; Unit Count; Total Unit Count; Residential Units; Apartment Units; # Apartments; Total Apartments; Doors; Keys; Total Keys; Total Rooms; Total Beds</t>
         </is>
       </c>
     </row>
@@ -5357,6 +5357,147 @@
       <c r="I96" t="inlineStr">
         <is>
           <t>Total SF; Total Gross SF; Gross SF; Total Square Feet; Gross Square Feet; Total GLA; Rentable SF; Total Rentable SF; NRA; Net Rentable Area; RSF; Rentable Square Feet; Total RSF; Leasable SF; GLA; Total NRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Construction Loan</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Debt &amp; Leverage</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Total construction/renovation loan commitment (full draw amount, not just at-close funded)</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Acquisition model, loan agreement</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>projection</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>What is the debt structure?</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Construction Loan; Senior Construction Loan; Construction Loan Proceeds; Construction Financing; Build Loan; Renovation Loan; Construction Facility</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Hard Costs</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Investment Basis</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Direct construction / renovation costs (labor, materials, contractor fees)</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Acquisition model, construction budget</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>projection</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>What is the total project cost?</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Hard Costs; Total Hard Costs; Construction Costs; Direct Costs; Hard Cost Budget; GC Costs; Contractor Costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Soft Costs</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Investment Basis</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Indirect project costs: architecture, engineering, permits, legal, FF&amp;E, etc.</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Acquisition model, construction budget</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>projection</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>What is the total project cost?</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Soft Costs; Total Soft Costs; Indirect Costs; Soft Cost Budget; A&amp;E Costs; Architecture &amp; Engineering; Professional Fees</t>
         </is>
       </c>
     </row>

--- a/Snapshot Metric.xlsx
+++ b/Snapshot Metric.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q104"/>
+  <dimension ref="A1:R109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,6 +514,11 @@
           <t>in_bounded_list</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>applies_to_property_types</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -781,7 +786,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Initial CapEx Budget; CapEx; Capital Expenditure; Capital Costs; Renovation Budget; Improvement Budget; Capital Improvements Budget; Capital Budget; CapEx Plan; Planned CapEx; Budgeted CapEx</t>
+          <t>Initial CapEx Budget; CapEx Budget; Total CapEx; Total Capital Expenditure; CapEx; Capital Expenditure; Capital Costs; Renovation Cost; Renovation Budget; Total Renovation Cost; Capital Plan; Total Capital Plan; CapEx Total; Capital Improvement Budget; Total Capital Improvements</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2667,7 +2672,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Physical Occupancy; Occupancy Rate; Physical Occ; Current Occupancy; Occupied Units; Physical Occ %</t>
+          <t>Physical Occupancy; Occupancy Rate; Physical Occ; Current Occupancy; Occupied Units; Physical Occ %; Occupancy %; Occ %; % Occupied; Occupancy at Acquisition; In-Place Occupancy; Stabilized Occupancy; Occupancy</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -5101,7 +5106,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Interest Rate</t>
+          <t>Interest Rate; All-in Rate; All-in Interest Rate; Coupon; Coupon Rate; Pay Rate; Effective Rate; Loan Rate; Note Rate; Stated Rate; Fixed Rate; Floating Rate; Total Interest Rate</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -5253,7 +5258,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Interest-Only Period Remaining</t>
+          <t>Interest-Only Period Remaining; I/O Period; IO Period; Interest Only Period; I/O Months; IO Months; I/O Term; IO Term; Interest-Only Term; Interest Only; I/O; IO</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7215,7 +7220,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Hold Period; Holding Period; Investment Period; Project Timeline; Total Project Timeline; Investment Horizon; Hold; Duration; Project Duration</t>
+          <t>Hold Period; Holding Period; Investment Period; Hold Term; Investment Horizon; Years Held; Hold (Years); Holding Period (Years); Total Hold; Total Hold Period</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -7398,6 +7403,11 @@
       </c>
       <c r="Q96" t="b">
         <v>1</v>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>Office; Multifamily; Industrial; Retail; Mixed-use; Self-Storage; Senior Living</t>
+        </is>
       </c>
     </row>
     <row r="97">
@@ -7957,6 +7967,374 @@
         </is>
       </c>
       <c r="Q104" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Number of Properties</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Investment Basis</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Number of distinct assets / properties in this deal (1 for single-asset, 2+ for portfolio)</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>General Information, Investment Summary</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Is this a single-asset or portfolio deal?</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Number of Properties; Number of Properties/Assets; # of Properties; # of Assets; Number of Hotels; # of Hotels; Number of Buildings; Property Count; Asset Count</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>1</v>
+      </c>
+      <c r="O105" t="n">
+        <v>100</v>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>general info; investment summary; one pager</t>
+        </is>
+      </c>
+      <c r="Q105" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Purchase Date</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Investment Basis</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Acquisition / closing date</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>General Information, Investment Summary</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>When was the deal closed?</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Purchase Date; Acquisition Date; Closing Date; Close Date; Deal Close; Investment Date</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>at_close</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>general info; investment summary; key uw</t>
+        </is>
+      </c>
+      <c r="Q106" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Exit Date</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Valuation &amp; Returns</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Projected disposition / exit / sale date</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>General Information, Key UW Metrics, Returns</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>projection</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>When does the model exit?</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Exit Date; Disposition Date; Sale Date; Reversion Date; Year of Exit; Disposition Year</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>exit</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>general info; investment summary; key uw; returns</t>
+        </is>
+      </c>
+      <c r="Q107" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Interest Rate Spread</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Debt &amp; Leverage</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Spread over the benchmark index (LIBOR / SOFR) for floating-rate debt</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Debt, Debt Information</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>projection</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>What is the floating-rate spread?</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Spread; Interest Rate Spread; Spread Over LIBOR; Spread Over SOFR; Spread Over Index; Loan Spread; Debt Spread</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>at_close</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>debt; debt information</t>
+        </is>
+      </c>
+      <c r="Q108" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Interest Rate Cap</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Debt &amp; Leverage</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Strike rate of the interest rate cap hedge (max benchmark rate hedged)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Debt, Debt Information</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>projection</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>What's the cap on floating-rate exposure?</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Interest Rate Cap; Rate Cap; Cap Strike; LIBOR Cap; SOFR Cap; Hedge Cap; Strike Rate</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>at_close</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>debt; debt information</t>
+        </is>
+      </c>
+      <c r="Q109" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Snapshot Metric.xlsx
+++ b/Snapshot Metric.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U109"/>
+  <dimension ref="A1:U110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8777,6 +8777,99 @@
         </is>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Loan-to-Cost (LTC)</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Debt &amp; Leverage</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Loan-to-Cost — debt as a percentage of TOTAL PROJECT COST. The relevant leverage metric for development / value-add deals financed on cost (where LTV may be absent). Distinct from LTV (debt / value).</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Debt, Sources &amp; Uses, Summary</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>projection</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>How is the deal levered on cost?</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Loan-to-Cost; LTC; Loan to Cost; Debt to Cost; Leverage (Cost)</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>at_close</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>debt; sources &amp; uses; summary; inputs</t>
+        </is>
+      </c>
+      <c r="Q110" t="b">
+        <v>1</v>
+      </c>
+      <c r="R110" t="inlineStr"/>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>leverage</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>debt; sources_uses; summary; inputs</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>comps; sensitivity; market</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Snapshot Metric.xlsx
+++ b/Snapshot Metric.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>sources_uses; debt; summary</t>
+          <t>debt,inputs,summary</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>debt; sources_uses; summary</t>
+          <t>debt,inputs,summary</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -4948,6 +4948,11 @@
       <c r="Q61" t="b">
         <v>0</v>
       </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>debt,inputs,summary</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5018,6 +5023,11 @@
       <c r="Q62" t="b">
         <v>0</v>
       </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>debt,inputs,summary</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5106,7 +5116,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>debt; summary</t>
+          <t>debt,inputs,summary</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -5202,7 +5212,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>debt; summary; returns</t>
+          <t>debt,inputs,summary</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -5298,7 +5308,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>debt; inputs; summary</t>
+          <t>debt,inputs,summary</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7777,7 +7787,6 @@
       <c r="Q97" t="b">
         <v>1</v>
       </c>
-      <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr">
         <is>
           <t>leverage</t>
@@ -8886,7 +8895,7 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>debt; sources_uses; summary; inputs</t>
+          <t>debt,inputs,summary</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
